--- a/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès et maman sont dans la cour. Maman trace un petit cercle. Maman dit : voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Inès touche le ballon. Elle passe le ballon à maman. Maman le rend. Inès attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Maman dit : tu as passé. Chacun a un tour.</t>
+          <t>Inès et maman sont dans la cour. Maman trace un petit cercle. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Inès touche le ballon. Elle passe le ballon à maman. Maman le rend. Inès attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Tu as passé. Chacun a un tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès et maman sont dans la cour. Maman trace un petit cercle.
+maman|Voici l'espace du jeu. On se passe le ballon. Chacun a un tour.
+narrateur|Inès touche le ballon. Elle passe le ballon à maman. Maman le rend. Inès attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.
+maman|Tu as passé. Chacun a un tour.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le ballon. Inès boit une gorgée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 maman|Tu as passé. Chacun a un tour.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Inès joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Inès a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Maman range le ballon. Inès boit une gorgée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inès se passe le ballon</t>
+          <t>Victorina se passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La craie a laissé une poudre blanche. Victorina et maman se passent le ballon dans le cercle. Papa ouvre la porte. Chacun a un tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès et maman sont dans la cour. Maman trace un petit cercle. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Inès touche le ballon. Elle passe le ballon à maman. Maman le rend. Inès attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Tu as passé. Chacun a un tour.</t>
+          <t>La craie blanche a laissé une poudre sur les dalles. Un chat dort sur le muret. Sa queue bouge un tout petit peu. Une marelle attend, à moitié effacée. Les dalles sont tièdes. Papa ouvre la porte de la cour. Victorina, tu vois le chat ? Oui, maman. Il dort. On joue tout doux, alors. Le chat aime le calme. En ce moment, maman trace un petit cercle. La craie fait un bruit sec. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Victorina touche le ballon. Il est un peu mou. Il sent le soleil. Il est mou. Oui. On le passe. Elle passe le ballon à maman. Maman le rend. Victorina attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Le chat ouvre un œil, puis le referme. Tu restes dans le cercle ? Oui, papa. Tu as passé. Chacun a un tour. Chacun a un tour. Bravo, Victorina. Tu as fait du bon travail. Encore un passage ? Oui. Victorina passe le ballon. Maman le rend encore. La poudre de craie colle aux chaussures. Le cercle est encore blanc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès et maman sont dans la cour. Maman trace un petit cercle.
-maman|Voici l'espace du jeu. On se passe le ballon. Chacun a un tour.
-narrateur|Inès touche le ballon. Elle passe le ballon à maman. Maman le rend. Inès attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.
-maman|Tu as passé. Chacun a un tour.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La craie blanche a laissé une poudre sur les dalles.
+narrateur|Un chat dort sur le muret.
+narrateur|Sa queue bouge un tout petit peu.
+narrateur|Une marelle attend, à moitié effacée.
+narrateur|Les dalles sont tièdes.
+narrateur|Papa ouvre la porte de la cour.
+maman|Victorina, tu vois le chat ?
+enfant-f|Oui, maman.
+enfant-f|Il dort.
+maman|On joue tout doux, alors.
+papa|Le chat aime le calme.
+narrateur|En ce moment, maman trace un petit cercle.
+narrateur|La craie fait un bruit sec.
+maman|Voici l'espace du jeu.
+maman|On se passe le ballon.
+maman|Chacun a un tour.
+narrateur|Victorina touche le ballon.
+narrateur|Il est un peu mou.
+narrateur|Il sent le soleil.
+enfant-f|Il est mou.
+maman|Oui.
+maman|On le passe.
+narrateur|Elle passe le ballon à maman.
+narrateur|Maman le rend.
+narrateur|Victorina attend son tour.
+narrateur|Puis elle passe encore.
+narrateur|Les pieds restent dans l'espace du jeu.
+narrateur|Le chat ouvre un œil, puis le referme.
+papa|Tu restes dans le cercle ?
+enfant-f|Oui, papa.
+maman|Tu as passé.
+maman|Chacun a un tour.
+enfant-f|Chacun a un tour.
+maman|Bravo, Victorina.
+maman|Tu as fait du bon travail.
+papa|Encore un passage ?
+enfant-f|Oui.
+narrateur|Victorina passe le ballon.
+narrateur|Maman le rend encore.
+narrateur|La poudre de craie colle aux chaussures.
+narrateur|Le cercle est encore blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1391,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès joue au ballon. Que fait-elle ?</t>
+          <t>Victorina joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,10 +1547,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès joue au ballon. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorina joue au ballon.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,7 +1575,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
+          <t>Victorina a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Chacun a un tour. Tu es restée dans le cercle ? Oui, papa. Bravo. Le ballon a un peu de craie dessus. Les dalles sont tièdes encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,10 +1719,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina a passé le ballon.
+narrateur|Elle a attendu son tour.
+narrateur|Dans l'espace du jeu.
+maman|Tu as attendu ton tour ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|Chacun a un tour.
+papa|Tu es restée dans le cercle ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Le ballon a un peu de craie dessus.
+narrateur|Les dalles sont tièdes encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,7 +1757,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le ballon. Inès boit une gorgée.</t>
+          <t>Maman range le ballon. Tu bois une gorgée ? Oui, maman. Victorina boit une gorgée. L'eau est fraîche. Tu as fini ta gorgée ? Oui. Bravo. Je ferme la porte ? Oui, papa. Le chat s'étire sur le muret.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1835,10 +1893,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le ballon. Inès boit une gorgée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman range le ballon.
+maman|Tu bois une gorgée ?
+enfant-f|Oui, maman.
+narrateur|Victorina boit une gorgée.
+narrateur|L'eau est fraîche.
+maman|Tu as fini ta gorgée ?
+enfant-f|Oui.
+maman|Bravo.
+papa|Je ferme la porte ?
+enfant-f|Oui, papa.
+narrateur|Le chat s'étire sur le muret.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,7 +1930,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le cercle de craie reste sur les dalles. Tu as passé le ballon. Chacun a un tour. Dans l'espace du jeu. Oui, maman. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2003,10 +2070,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le cercle de craie reste sur les dalles.
+maman|Tu as passé le ballon.
+maman|Chacun a un tour.
+papa|Dans l'espace du jeu.
+enfant-f|Oui, maman.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2134,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La craie blanche a laissé une poudre sur les dalles. Un chat dort sur le muret. Sa queue bouge un tout petit peu. Une marelle attend, à moitié effacée. Les dalles sont tièdes. Papa ouvre la porte de la cour. Victorina, tu vois le chat ? Oui, maman. Il dort. On joue tout doux, alors. Le chat aime le calme. En ce moment, maman trace un petit cercle. La craie fait un bruit sec. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Victorina touche le ballon. Il est un peu mou. Il sent le soleil. Il est mou. Oui. On le passe. Elle passe le ballon à maman. Maman le rend. Victorina attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Le chat ouvre un œil, puis le referme. Tu restes dans le cercle ? Oui, papa. Tu as passé. Chacun a un tour. Chacun a un tour. Bravo, Victorina. Tu as fait du bon travail. Encore un passage ? Oui. Victorina passe le ballon. Maman le rend encore. La poudre de craie colle aux chaussures. Le cercle est encore blanc.</t>
+          <t>La craie blanche a laissé une poudre sur les dalles. Un chat dort sur le muret. Sa queue bouge un tout petit peu. Une marelle attend, à moitié effacée. Les dalles sont tièdes. Une fourmi traverse une dalle. Le soleil fait un carré chaud. Papa ouvre la porte de la cour. La poignée est un peu rêche. Victorina, tu vois le chat ? Oui, maman. Il dort. On joue tout doux, alors. Le chat aime le calme. En ce moment, maman trace un petit cercle. La craie fait un bruit sec. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Victorina touche le ballon. Il est un peu mou. Il sent le soleil. Il est mou. Oui. On le passe. Elle passe le ballon à maman. Maman le rend. Victorina attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Le chat ouvre un œil, puis le referme. Tu restes dans le cercle ? Oui, papa. Tu as passé. Chacun a un tour. Chacun a un tour. Bravo, Victorina. Encore un passage ? Oui. Victorina passe le ballon. Maman le rend encore. La poudre de craie colle aux chaussures. Le cercle est encore blanc. La fourmi est partie. Oui. Le chat dort toujours. La marelle attend encore. Les dalles restent tièdes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès et maman sont dans la cour. Maman trace un petit cercle. Maman dit : voici l'espace du jeu. On se passe le ballon. Chacun a un &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Inès touche le ballon. Elle passe le ballon à maman. Maman le rend. Inès attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Maman dit : tu as passé. Chacun a un tour.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La craie blanche a laissé une poudre sur les dalles. Un chat dort sur le muret. Sa queue bouge un tout petit peu. Une marelle attend, à moitié effacée. Les dalles sont tièdes. Une fourmi traverse une dalle. Le soleil fait un carré chaud. Papa ouvre la porte de la cour. La poignée est un peu rêche. Victorina, tu vois le chat ? Oui, maman. Il dort. On joue tout doux, alors. Le chat aime le calme. En ce moment, maman trace un petit cercle. La craie fait un bruit sec. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Victorina touche le ballon. Il est un peu mou. Il sent le soleil. Il est mou. Oui. On le passe. Elle passe le ballon à maman. Maman le rend. Victorina attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu. Le chat ouvre un œil, puis le referme. Tu restes dans le cercle ? Oui, papa. Tu as passé. Chacun a un tour. Chacun a un tour. Bravo, Victorina. Encore un passage ? Oui. Victorina passe le ballon. Maman le rend encore. La poudre de craie colle aux chaussures. Le cercle est encore blanc. La fourmi est partie. Oui. Le chat dort toujours. La marelle attend encore. Les dalles restent tièdes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,7 +1329,10 @@
 narrateur|Sa queue bouge un tout petit peu.
 narrateur|Une marelle attend, à moitié effacée.
 narrateur|Les dalles sont tièdes.
+narrateur|Une fourmi traverse une dalle.
+narrateur|Le soleil fait un carré chaud.
 narrateur|Papa ouvre la porte de la cour.
+narrateur|La poignée est un peu rêche.
 maman|Victorina, tu vois le chat ?
 enfant-f|Oui, maman.
 enfant-f|Il dort.
@@ -1358,13 +1361,17 @@
 maman|Chacun a un tour.
 enfant-f|Chacun a un tour.
 maman|Bravo, Victorina.
-maman|Tu as fait du bon travail.
 papa|Encore un passage ?
 enfant-f|Oui.
 narrateur|Victorina passe le ballon.
 narrateur|Maman le rend encore.
 narrateur|La poudre de craie colle aux chaussures.
-narrateur|Le cercle est encore blanc.</t>
+narrateur|Le cercle est encore blanc.
+maman|La fourmi est partie.
+enfant-f|Oui.
+papa|Le chat dort toujours.
+narrateur|La marelle attend encore.
+narrateur|Les dalles restent tièdes.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès joue au ballon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,12 +1582,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Chacun a un tour. Tu es restée dans le cercle ? Oui, papa. Bravo. Le ballon a un peu de craie dessus. Les dalles sont tièdes encore.</t>
+          <t>Victorina a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Chacun a un tour. Tu es restée dans le cercle ? Oui, papa. Bravo. Le ballon a un peu de craie dessus. Les dalles sont tièdes encore. On reprend un tour ? Oui, maman. Victorina attend. Puis elle passe. Bien joué. Le chat dort encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès a passé le ballon. Elle a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Chacun a un tour. Tu es restée dans le cercle ? Oui, papa. Bravo. Le ballon a un peu de craie dessus. Les dalles sont tièdes encore. On reprend un tour ? Oui, maman. Victorina attend. Puis elle passe. Bien joué. Le chat dort encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1730,7 +1737,13 @@
 enfant-f|Oui, papa.
 papa|Bravo.
 narrateur|Le ballon a un peu de craie dessus.
-narrateur|Les dalles sont tièdes encore.</t>
+narrateur|Les dalles sont tièdes encore.
+maman|On reprend un tour ?
+enfant-f|Oui, maman.
+narrateur|Victorina attend.
+narrateur|Puis elle passe.
+papa|Bien joué.
+narrateur|Le chat dort encore.</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le ballon. Tu bois une gorgée ? Oui, maman. Victorina boit une gorgée. L'eau est fraîche. Tu as fini ta gorgée ? Oui. Bravo. Je ferme la porte ? Oui, papa. Le chat s'étire sur le muret.</t>
+          <t>Maman range le ballon. Tu bois une gorgée ? Oui, maman. Victorina boit une gorgée. L'eau est fraîche. Tu as fini ta gorgée ? Oui. Bravo. Je ferme la porte ? Oui, papa. Le chat s'étire sur le muret. Il a chaud, le chat. Il est doux. On le laisse dormir.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le ballon. Inès boit une gorgée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range le ballon. Tu bois une gorgée ? Oui, maman. Victorina boit une gorgée. L'eau est fraîche. Tu as fini ta gorgée ? Oui. Bravo. Je ferme la porte ? Oui, papa. Le chat s'étire sur le muret. Il a chaud, le chat. Il est doux. On le laisse dormir.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1903,7 +1916,10 @@
 maman|Bravo.
 papa|Je ferme la porte ?
 enfant-f|Oui, papa.
-narrateur|Le chat s'étire sur le muret.</t>
+narrateur|Le chat s'étire sur le muret.
+papa|Il a chaud, le chat.
+enfant-f|Il est doux.
+maman|On le laisse dormir.</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le cercle de craie reste sur les dalles. Tu as passé le ballon. Chacun a un tour. Dans l'espace du jeu. Oui, maman. L'histoire est finie.</t>
+          <t>Le cercle de craie reste sur les dalles. Tu as passé le ballon. Chacun a un tour. Dans l'espace du jeu. Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cercle de craie reste sur les dalles. Tu as passé le ballon. Chacun a un tour. Dans l'espace du jeu. Oui, maman.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2074,8 +2090,7 @@
 maman|Tu as passé le ballon.
 maman|Chacun a un tour.
 papa|Dans l'espace du jeu.
-enfant-f|Oui, maman.
-narrateur|L'histoire est finie.</t>
+enfant-f|Oui, maman.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2141,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour</t>
+          <t>cour, craie, chat sur le muret, cercle</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, maman</t>
+          <t>Victorina, maman, papa</t>
         </is>
       </c>
     </row>
